--- a/24_DS_Gen_Ahm_1/01_Advanced Excel/Oct11.xlsx
+++ b/24_DS_Gen_Ahm_1/01_Advanced Excel/Oct11.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\Batches\24_DS_Gen_Ahm_1\Advanced Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\24_DS_Gen_Ahm_1\01_Advanced Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED78A1A3-DD92-4904-BE24-670AD1478AFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EC31AD9-2A7A-4639-AD3B-914564DE8D58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="58">
   <si>
     <t>First Name</t>
   </si>
@@ -187,6 +187,18 @@
   </si>
   <si>
     <t>Status</t>
+  </si>
+  <si>
+    <t>Hi Hetal</t>
+  </si>
+  <si>
+    <t>Hi Namrata</t>
+  </si>
+  <si>
+    <t>Hello Ms Jani</t>
+  </si>
+  <si>
+    <t>Hello Ms Raval</t>
   </si>
 </sst>
 </file>
@@ -227,7 +239,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="-0.249977111117893"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -298,11 +310,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -318,7 +326,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -599,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -609,52 +621,52 @@
     <col min="9" max="9" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="4.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9"/>
-      <c r="H1" s="10" t="s">
+      <c r="D1" s="7"/>
+      <c r="H1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
+    <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
       <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -680,9 +692,15 @@
       <c r="K3" s="2">
         <v>24</v>
       </c>
-      <c r="L3" s="2"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L3" s="2" t="str">
+        <f>IF(K3&lt;18, _xlfn.CONCAT("Hi ", H3), _xlfn.CONCAT("Hello ", J3, " ", I3))</f>
+        <v>Hello Ms Jani</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -708,9 +726,15 @@
       <c r="K4" s="2">
         <v>43</v>
       </c>
-      <c r="L4" s="2"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L4" s="2" t="str">
+        <f t="shared" ref="L4:L10" si="1">IF(K4&lt;18, _xlfn.CONCAT("Hi ", H4), _xlfn.CONCAT("Hello ", J4, " ", I4))</f>
+        <v>Hello Ms Raval</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
@@ -736,9 +760,13 @@
       <c r="K5" s="2">
         <v>50</v>
       </c>
-      <c r="L5" s="2"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L5" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Hello Mr Seth</v>
+      </c>
+      <c r="M5" s="2"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
@@ -764,9 +792,15 @@
       <c r="K6" s="2">
         <v>14</v>
       </c>
-      <c r="L6" s="2"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L6" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Hi Hetal</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -792,9 +826,13 @@
       <c r="K7" s="2">
         <v>27</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L7" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Hello Dr Panchal</v>
+      </c>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
@@ -820,9 +858,13 @@
       <c r="K8" s="2">
         <v>30</v>
       </c>
-      <c r="L8" s="2"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L8" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Hello Prof Tewar</v>
+      </c>
+      <c r="M8" s="2"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
@@ -848,9 +890,15 @@
       <c r="K9" s="2">
         <v>15</v>
       </c>
-      <c r="L9" s="2"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L9" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Hi Namrata</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
@@ -876,43 +924,44 @@
       <c r="K10" s="2">
         <v>17</v>
       </c>
-      <c r="L10" s="2"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="3"/>
-      <c r="B14" s="5" t="s">
+      <c r="L10" s="2" t="str">
+        <f t="shared" si="1"/>
+        <v>Hi Hitesh</v>
+      </c>
+      <c r="M10" s="2"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" s="9"/>
+      <c r="B14" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="4">
-        <v>-4</v>
-      </c>
-      <c r="D14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
-      <c r="B15" s="5" t="s">
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" s="9"/>
+      <c r="B15" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="6" t="str">
-        <f>IF(C14&gt;0, "Positive", IF(C14=0, "Zero", "Negative"))</f>
-        <v>Negative</v>
-      </c>
-      <c r="D15" s="11" t="str">
-        <f>_xlfn.IFS(C14&gt;0, "Positive", C14&lt;0, "Negative", C14=0, "Zero")</f>
-        <v>Negative</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
+      <c r="C15" s="4" t="str">
+        <f>IF(C14&lt;0, "Negative", IF(C14&gt;0, "Positive", "Zero"))</f>
+        <v>Zero</v>
+      </c>
+      <c r="D15" s="11"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="8">
